--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484047_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484047_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5948</v>
+        <v>11.3281</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6759</v>
+        <v>10.9423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.3859</v>
       </c>
       <c r="G2" t="n">
         <v>7.1802</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3903</v>
+        <v>1.1236</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4479</v>
+        <v>0.7143</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9424</v>
+        <v>0.4093</v>
       </c>
       <c r="V2" t="n">
         <v>3.6194</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3084</v>
+        <v>2.2355</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6849</v>
+        <v>3.1351</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3765</v>
+        <v>-0.8996</v>
       </c>
       <c r="G3" t="n">
         <v>-1.6072</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>0.114</v>
+        <v>0.0411</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1905</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0765</v>
+        <v>-0.5995</v>
       </c>
       <c r="V3" t="n">
         <v>2.4129</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1194</v>
+        <v>1.0633</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0789</v>
+        <v>2.2401</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1983</v>
+        <v>-1.1768</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8372000000000001</v>
+        <v>1.8843</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8542</v>
+        <v>2.8171</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.017</v>
+        <v>-0.9328</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1818</v>
+        <v>1.9207</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7674</v>
+        <v>2.6008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4144</v>
+        <v>-0.6802</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3446</v>
+        <v>-0.0363</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9132</v>
+        <v>0.2163</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4314</v>
+        <v>-0.2526</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.9596</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9758</v>
+        <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2021</v>
+        <v>0.5838</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6349</v>
+        <v>0.4422</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5672</v>
+        <v>0.1416</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0639</v>
+        <v>-1.2065</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0639</v>
+        <v>0.8692</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0633</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2401</v>
+        <v>-0.0166</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1768</v>
+        <v>0.8336</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8843</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8171</v>
+        <v>1.8542</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9328</v>
+        <v>-1.017</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9207</v>
+        <v>3.1818</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6008</v>
+        <v>2.7674</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6802</v>
+        <v>0.4144</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0363</v>
+        <v>-2.3446</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2163</v>
+        <v>-0.9132</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2526</v>
+        <v>-1.4314</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-4.9596</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>2.9758</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5838</v>
+        <v>0.8998</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4422</v>
+        <v>0.6973</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1416</v>
+        <v>0.2025</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>1.0639</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8692</v>
+        <v>1.0639</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.958</v>
+        <v>-2.6815</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3156</v>
+        <v>-1.1512</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6425</v>
+        <v>-1.5303</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4264</v>
@@ -922,13 +922,13 @@
         <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1349</v>
+        <v>0.1417</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1191</v>
+        <v>0.2835</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.254</v>
+        <v>-0.1418</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6032</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.0078</v>
+        <v>-2.8573</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2569</v>
+        <v>-3.3589</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2491</v>
+        <v>0.5016</v>
       </c>
       <c r="G7" t="n">
         <v>0.7349</v>
@@ -1000,13 +1000,13 @@
         <v>2.7774</v>
       </c>
       <c r="S7" t="n">
-        <v>0.106</v>
+        <v>0.2565</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6859</v>
+        <v>0.5839</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.58</v>
+        <v>-0.3275</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6745</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0016</v>
+        <v>-4.0719</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3559</v>
+        <v>-2.0895</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6457</v>
+        <v>-1.9824</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2961</v>
@@ -1078,13 +1078,13 @@
         <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0962</v>
+        <v>1.0259</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4366</v>
+        <v>0.703</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6596</v>
+        <v>0.3229</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8097</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.1512</v>
+        <v>-6.5543</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9213</v>
+        <v>-4.7173</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2298</v>
+        <v>-1.8371</v>
       </c>
       <c r="G9" t="n">
         <v>-5.1527</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2483</v>
+        <v>0.3486</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.2722</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3164</v>
+        <v>0.0764</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1469</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.032700000000002</v>
+        <v>-0.7210999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>4.672300000000003</v>
+        <v>4.983999999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.705</v>
+        <v>-5.7051</v>
       </c>
       <c r="G10" t="n">
         <v>0.1542000000000012</v>
@@ -1234,13 +1234,13 @@
         <v>15.8707</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1092</v>
+        <v>4.420999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>4.0252</v>
+        <v>4.337</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08390000000000009</v>
+        <v>0.08389999999999992</v>
       </c>
       <c r="V10" t="n">
         <v>0.6554000000000011</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.4636</v>
+        <v>11.4578</v>
       </c>
       <c r="E11" t="n">
-        <v>11.093</v>
+        <v>9.5626</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3706</v>
+        <v>1.8952</v>
       </c>
       <c r="G11" t="n">
         <v>6.4801</v>
@@ -1312,13 +1312,13 @@
         <v>3.7693</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4721</v>
+        <v>0.4663</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1144</v>
+        <v>0.584</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6423</v>
+        <v>-0.1177</v>
       </c>
       <c r="V11" t="n">
         <v>0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2967</v>
+        <v>2.3433</v>
       </c>
       <c r="E12" t="n">
-        <v>0.985</v>
+        <v>1.6993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3116</v>
+        <v>0.644</v>
       </c>
       <c r="G12" t="n">
         <v>1.2738</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0367</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5498</v>
+        <v>0.1644</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4869</v>
+        <v>-0.1545</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.278</v>
+        <v>2.1282</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0548</v>
+        <v>2.769</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7768</v>
+        <v>-0.6408</v>
       </c>
       <c r="G13" t="n">
         <v>1.0144</v>
@@ -1468,13 +1468,13 @@
         <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6688</v>
+        <v>0.1814</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3627</v>
+        <v>0.3515</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3061</v>
+        <v>-0.1701</v>
       </c>
       <c r="V13" t="n">
         <v>0.3373</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>M. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3159</v>
+        <v>0.9635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06950000000000001</v>
+        <v>1.9011</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2465</v>
+        <v>-0.9377</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1238</v>
+        <v>0.107</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1108</v>
+        <v>2.2434</v>
       </c>
       <c r="I14" t="n">
-        <v>0.013</v>
+        <v>-2.1365</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4436</v>
+        <v>1.9399</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4436</v>
+        <v>3.9729</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-2.0329</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3198</v>
+        <v>-1.833</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3328</v>
+        <v>-1.7294</v>
       </c>
       <c r="O14" t="n">
-        <v>0.013</v>
+        <v>-0.1035</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1903</v>
+        <v>2.7774</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9982</v>
+        <v>-1.2824</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3741</v>
+        <v>-0.8728</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6241</v>
+        <v>-0.4096</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5437</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.0162</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GARCIA CALVO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0189</v>
+        <v>0.5021</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2889</v>
+        <v>0.1715</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2701</v>
+        <v>0.3306</v>
       </c>
       <c r="G15" t="n">
-        <v>0.107</v>
+        <v>0.1238</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2434</v>
+        <v>0.1108</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1365</v>
+        <v>0.013</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9399</v>
+        <v>0.4436</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9729</v>
+        <v>0.4436</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.0329</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.833</v>
+        <v>-0.3198</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7294</v>
+        <v>-0.3328</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1035</v>
+        <v>0.013</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7774</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.227</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4849</v>
+        <v>-0.272</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7421</v>
+        <v>-0.5399</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5437</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0162</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1359</v>
+        <v>-0.4005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0767</v>
+        <v>2.0441</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2126</v>
+        <v>-2.4446</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2692</v>
+        <v>0.7474</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1719</v>
+        <v>-2.2375</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0973</v>
+        <v>2.985</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0365</v>
+        <v>2.4016</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8357</v>
+        <v>-0.2918</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2008</v>
+        <v>2.6934</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7674</v>
+        <v>-1.6541</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6638</v>
+        <v>-1.9457</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1035</v>
+        <v>0.2916</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1741</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7774</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2743</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1869</v>
+        <v>0.3685</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.3019</v>
       </c>
       <c r="V16" t="n">
+        <v>-1.8097</v>
+      </c>
+      <c r="W16" t="n">
         <v>0.266</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.4012</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.1352</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7227</v>
+        <v>-0.6325</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9421</v>
+        <v>-0.3314</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6648</v>
+        <v>-0.301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7474</v>
+        <v>0.2692</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2375</v>
+        <v>0.1719</v>
       </c>
       <c r="I17" t="n">
-        <v>2.985</v>
+        <v>0.0973</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4016</v>
+        <v>2.0365</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2918</v>
+        <v>1.8357</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6934</v>
+        <v>0.2008</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6541</v>
+        <v>-1.7674</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9457</v>
+        <v>-1.6638</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2916</v>
+        <v>-0.1035</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5952</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>2.7774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2556</v>
+        <v>-0.7708</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2665</v>
+        <v>-0.595</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5221</v>
+        <v>-0.1758</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>1.4012</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.0757</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0259</v>
+        <v>-2.7292</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4845</v>
+        <v>-2.3146</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5414</v>
+        <v>-0.4145</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8205</v>
+        <v>-1.2838</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.8055</v>
+        <v>-1.3305</v>
       </c>
       <c r="I18" t="n">
-        <v>3.9851</v>
+        <v>0.0467</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0368</v>
+        <v>-0.6199</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.655</v>
+        <v>-0.66</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6182</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7836</v>
+        <v>-0.6639</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.1505</v>
+        <v>-0.6704</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3669</v>
+        <v>0.0065</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.5871</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.3968</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.1822</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.579</v>
-      </c>
       <c r="S18" t="n">
-        <v>2.0054</v>
+        <v>0.1417</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7346</v>
+        <v>0.2891</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2708</v>
+        <v>-0.1474</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.6076</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.6076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4129</v>
+        <v>-3.3029</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1106</v>
+        <v>-1.5047</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3023</v>
+        <v>-1.7982</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2838</v>
+        <v>-1.8205</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3305</v>
+        <v>-5.8055</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0467</v>
+        <v>3.9851</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6199</v>
+        <v>-0.0368</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.66</v>
+        <v>-2.655</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>2.6182</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6639</v>
+        <v>-1.7836</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6704</v>
+        <v>-3.1505</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0065</v>
+        <v>1.3669</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3968</v>
+        <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.458</v>
+        <v>0.7284</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4932</v>
+        <v>0.7143</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0352</v>
+        <v>0.0141</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.6076</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.6076</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1196</v>
+        <v>-3.7336</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7827</v>
+        <v>-3.4766</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.337</v>
+        <v>-0.257</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1607</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.3826</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2698</v>
+        <v>-0.1899</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9233</v>
+        <v>-4.2032</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4275</v>
+        <v>-4.8153</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5041</v>
+        <v>0.6121</v>
       </c>
       <c r="G21" t="n">
         <v>-4.905</v>
@@ -2092,13 +2092,13 @@
         <v>2.579</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8155</v>
+        <v>-1.0954</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2356</v>
+        <v>-0.6234</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.58</v>
+        <v>-0.472</v>
       </c>
       <c r="V21" t="n">
         <v>0.4085</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.032799999999997</v>
+        <v>2.393000000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>5.704700000000001</v>
+        <v>5.705000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6722</v>
+        <v>-3.3119</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1543000000000001</v>
@@ -2146,7 +2146,7 @@
         <v>14.2974</v>
       </c>
       <c r="K22" t="n">
-        <v>5.877599999999999</v>
+        <v>5.877600000000001</v>
       </c>
       <c r="L22" t="n">
         <v>8.420199999999999</v>
@@ -2170,19 +2170,19 @@
         <v>21.8224</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.1092</v>
+        <v>-2.7489</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08410000000000006</v>
+        <v>-0.08409999999999995</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.0252</v>
+        <v>-2.6647</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6552999999999997</v>
+        <v>-0.6552999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>7.362399999999999</v>
+        <v>7.3624</v>
       </c>
       <c r="X22" t="n">
         <v>-8.0176</v>
